--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 08/02. Trả bảo hành/TBH_NhatQuang_270826.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 08/02. Trả bảo hành/TBH_NhatQuang_270826.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 08\02. Trả bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D711EF55-3A05-4406-98C5-2C144A2D8CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{956D9F9C-53DC-49D1-9396-DC4A3E215D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -499,6 +499,30 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -516,30 +540,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -925,72 +925,72 @@
       <c r="A1" s="37"/>
       <c r="B1" s="38"/>
       <c r="C1" s="39"/>
-      <c r="D1" s="53" t="s">
+      <c r="D1" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40"/>
       <c r="C2" s="41"/>
-      <c r="D2" s="55" t="s">
+      <c r="D2" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="56"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="40"/>
       <c r="C3" s="41"/>
-      <c r="D3" s="57" t="s">
+      <c r="D3" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="58"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="52"/>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="42"/>
       <c r="B4" s="43"/>
       <c r="C4" s="44"/>
-      <c r="D4" s="59" t="s">
+      <c r="D4" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="60"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="54"/>
     </row>
     <row r="5" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
     </row>
     <row r="6" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
+      <c r="B6" s="57"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
       <c r="E6" s="10"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
@@ -1000,12 +1000,12 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
+      <c r="B7" s="57"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="57"/>
       <c r="E7" s="10"/>
       <c r="F7" s="12"/>
       <c r="G7" s="12"/>
@@ -1013,12 +1013,12 @@
       <c r="I7" s="12"/>
     </row>
     <row r="8" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
       <c r="E8" s="10"/>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
@@ -1026,12 +1026,12 @@
       <c r="I8" s="11"/>
     </row>
     <row r="9" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="49" t="s">
+      <c r="A9" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
       <c r="E9" s="10"/>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
@@ -1108,34 +1108,34 @@
       <c r="I12" s="9"/>
     </row>
     <row r="13" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="52" t="s">
+      <c r="A13" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
+      <c r="B13" s="60"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
       <c r="E13" s="24"/>
       <c r="F13" s="25"/>
-      <c r="G13" s="50" t="s">
+      <c r="G13" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="50"/>
-      <c r="I13" s="50"/>
+      <c r="H13" s="58"/>
+      <c r="I13" s="58"/>
     </row>
     <row r="14" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="51" t="s">
+      <c r="A14" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="51"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
+      <c r="B14" s="59"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
       <c r="E14" s="8"/>
       <c r="F14" s="7"/>
-      <c r="G14" s="51" t="s">
+      <c r="G14" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="59"/>
     </row>
     <row r="15" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="27"/>
@@ -1182,19 +1182,19 @@
       <c r="I18" s="34"/>
     </row>
     <row r="19" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="52" t="s">
+      <c r="A19" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="52"/>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="60"/>
       <c r="E19" s="24"/>
       <c r="F19" s="20"/>
-      <c r="G19" s="52" t="s">
+      <c r="G19" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="H19" s="52"/>
-      <c r="I19" s="52"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="60"/>
     </row>
     <row r="20" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="20"/>
@@ -1208,28 +1208,28 @@
       <c r="I20" s="36"/>
     </row>
     <row r="22" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B22" s="48"/>
-      <c r="C22" s="48"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="56"/>
     </row>
     <row r="61" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A9:D9"/>
     <mergeCell ref="G13:I13"/>
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="G19:I19"/>
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A13:D13"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="D4:I4"/>
+    <mergeCell ref="A5:I5"/>
   </mergeCells>
   <pageMargins left="1.2" right="1.2" top="1.5" bottom="1.5" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="91" orientation="landscape" r:id="rId1"/>
